--- a/data/trans_bre/P1423-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,45</t>
+          <t>2,04; 6,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 12,26</t>
+          <t>6,24; 12,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 11,85</t>
+          <t>6,52; 11,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,71</t>
+          <t>-0,22; 5,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,43; 397,86</t>
+          <t>59,95; 377,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>135,04; 449,49</t>
+          <t>128,58; 434,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>162,85; 634,76</t>
+          <t>162,99; 647,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 93,78</t>
+          <t>-2,86; 92,13</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,01</t>
+          <t>2,85; 6,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,31</t>
+          <t>4,08; 9,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,77</t>
+          <t>4,67; 8,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,26</t>
+          <t>5,39; 10,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,86; 314,7</t>
+          <t>73,28; 336,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,67; 238,63</t>
+          <t>68,29; 246,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>157,65; 553,69</t>
+          <t>163,1; 574,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>104,76; 495,35</t>
+          <t>104,39; 500,59</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,66</t>
+          <t>2,07; 6,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,76</t>
+          <t>4,05; 9,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,34</t>
+          <t>3,18; 8,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 8,74</t>
+          <t>-1,93; 8,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,84; 250,25</t>
+          <t>36,8; 248,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,22; 423,38</t>
+          <t>90,53; 453,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,77; 303,17</t>
+          <t>59,75; 281,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 182,61</t>
+          <t>-22,6; 167,52</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,74</t>
+          <t>2,54; 6,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,29</t>
+          <t>4,3; 9,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,15</t>
+          <t>3,95; 8,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,73</t>
+          <t>2,04; 7,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,47; 230,91</t>
+          <t>58,44; 254,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,35; 257,56</t>
+          <t>72,22; 260,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,47; 261,98</t>
+          <t>69,97; 251,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,35; 131,86</t>
+          <t>27,23; 135,3</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,61</t>
+          <t>3,4; 5,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,42</t>
+          <t>6,01; 8,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,11</t>
+          <t>5,78; 8,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,9</t>
+          <t>3,37; 7,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>96,3; 209,38</t>
+          <t>95,87; 207,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>121,93; 235,6</t>
+          <t>129,22; 239,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>156,24; 293,11</t>
+          <t>153,38; 285,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,36; 143,15</t>
+          <t>56,85; 149,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1423-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,25</t>
+          <t>1,9; 6,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 12,13</t>
+          <t>6,12; 11,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,96</t>
+          <t>6,18; 11,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,73</t>
+          <t>1,11; 6,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,95; 377,59</t>
+          <t>54,41; 390,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>128,58; 434,28</t>
+          <t>129,33; 464,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>162,99; 647,45</t>
+          <t>165,43; 622,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 92,13</t>
+          <t>10,67; 104,53</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>203,17%</t>
+          <t>141,37%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,9</t>
+          <t>2,87; 7,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 9,33</t>
+          <t>4,13; 9,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,91</t>
+          <t>4,82; 9,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,55</t>
+          <t>4,61; 8,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,28; 336,46</t>
+          <t>71,0; 327,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,29; 246,22</t>
+          <t>68,57; 245,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>163,1; 574,24</t>
+          <t>169,35; 563,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>104,39; 500,59</t>
+          <t>75,73; 241,9</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>8,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>146,05%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,83</t>
+          <t>1,98; 6,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,57</t>
+          <t>3,93; 9,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,23</t>
+          <t>3,03; 8,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 8,63</t>
+          <t>5,19; 10,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,8; 248,53</t>
+          <t>40,1; 264,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,53; 453,99</t>
+          <t>82,95; 410,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,75; 281,74</t>
+          <t>55,36; 303,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 167,52</t>
+          <t>70,97; 258,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,51</t>
+          <t>2,23; 6,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,4</t>
+          <t>4,44; 9,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,98</t>
+          <t>4,23; 8,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,71</t>
+          <t>3,3; 8,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,44; 254,7</t>
+          <t>46,67; 237,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,22; 260,77</t>
+          <t>77,47; 255,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,97; 251,27</t>
+          <t>76,29; 272,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,23; 135,3</t>
+          <t>39,98; 140,61</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>100,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,59</t>
+          <t>3,38; 5,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,55</t>
+          <t>5,94; 8,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,17</t>
+          <t>5,69; 8,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,03</t>
+          <t>4,9; 7,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>95,87; 207,45</t>
+          <t>94,2; 210,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>129,22; 239,44</t>
+          <t>125,35; 236,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>153,38; 285,53</t>
+          <t>154,23; 286,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>56,85; 149,75</t>
+          <t>71,33; 133,31</t>
         </is>
       </c>
     </row>
